--- a/Config/Excel/BattleMapConfig.xlsx
+++ b/Config/Excel/BattleMapConfig.xlsx
@@ -684,11 +684,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -1014,11 +1011,10 @@
     <col min="7" max="7" width="20.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:8">
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1032,7 +1028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:8">
+    <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1048,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:8">
+    <row r="5" s="1" customFormat="1" spans="1:8">
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
@@ -1073,12 +1069,12 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E6">
@@ -1091,18 +1087,18 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:4">
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
+    <row r="7" spans="1:8">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
